--- a/public/member-import-template.xlsx
+++ b/public/member-import-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="人员名单" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,55 +397,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>ID</v>
+        <v>姓名</v>
       </c>
       <c r="B1" t="str">
-        <v>姓名</v>
-      </c>
-      <c r="C1" t="str">
-        <v>电话</v>
+        <v>手机号</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>U001</v>
+        <v>张三</v>
       </c>
       <c r="B2" t="str">
-        <v>张三</v>
-      </c>
-      <c r="C2" t="str">
         <v>13800000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>U002</v>
+        <v>李四</v>
       </c>
       <c r="B3" t="str">
-        <v>李四</v>
-      </c>
-      <c r="C3" t="str">
         <v>13800000002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>U003</v>
+        <v>王五</v>
       </c>
       <c r="B4" t="str">
-        <v>王五</v>
-      </c>
-      <c r="C4" t="str">
         <v>13800000003</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
   </ignoredErrors>
 </worksheet>
 </file>